--- a/排课结果/调课成功的排课失败课程.xlsx
+++ b/排课结果/调课成功的排课失败课程.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P251"/>
+  <dimension ref="A1:P253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9791,11 +9791,11 @@
         <v>100</v>
       </c>
       <c r="H132" t="n">
-        <v>305</v>
+        <v>406</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1054</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -10335,11 +10335,11 @@
         <v>90</v>
       </c>
       <c r="H140" t="n">
-        <v>406</v>
+        <v>3202</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>CLS1054</t>
+          <t>CLS1197</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -10403,11 +10403,11 @@
         <v>90</v>
       </c>
       <c r="H141" t="n">
-        <v>3202</v>
+        <v>3211</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>CLS1197</t>
+          <t>CLS1201</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -10675,11 +10675,11 @@
         <v>60</v>
       </c>
       <c r="H145" t="n">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>CLS1201</t>
+          <t>CLS1202</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -10879,11 +10879,11 @@
         <v>60</v>
       </c>
       <c r="H148" t="n">
-        <v>3212</v>
+        <v>3302</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>CLS1202</t>
+          <t>CLS1204</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -11015,11 +11015,11 @@
         <v>70</v>
       </c>
       <c r="H150" t="n">
-        <v>3302</v>
+        <v>3304</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>CLS1204</t>
+          <t>CLS1206</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -11083,11 +11083,11 @@
         <v>60</v>
       </c>
       <c r="H151" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>CLS1206</t>
+          <t>CLS1209</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -11151,11 +11151,11 @@
         <v>90</v>
       </c>
       <c r="H152" t="n">
-        <v>3308</v>
+        <v>3314</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>CLS1209</t>
+          <t>CLS1210</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -11491,11 +11491,11 @@
         <v>90</v>
       </c>
       <c r="H157" t="n">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1021</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -11559,11 +11559,11 @@
         <v>90</v>
       </c>
       <c r="H158" t="n">
-        <v>301</v>
+        <v>3315</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1211</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -11627,11 +11627,11 @@
         <v>90</v>
       </c>
       <c r="H159" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1029</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -11657,12 +11657,12 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
@@ -11695,11 +11695,11 @@
         <v>90</v>
       </c>
       <c r="H160" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1029</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
@@ -11831,11 +11831,11 @@
         <v>90</v>
       </c>
       <c r="H162" t="n">
-        <v>305</v>
+        <v>3407</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1215</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -11861,12 +11861,12 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -11899,11 +11899,11 @@
         <v>90</v>
       </c>
       <c r="H163" t="n">
-        <v>305</v>
+        <v>3404</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1213</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -11967,11 +11967,11 @@
         <v>90</v>
       </c>
       <c r="H164" t="n">
-        <v>305</v>
+        <v>501</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1021</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -11997,12 +11997,12 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
@@ -12035,11 +12035,11 @@
         <v>90</v>
       </c>
       <c r="H165" t="n">
-        <v>3314</v>
+        <v>3403</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>CLS1210</t>
+          <t>CLS1212</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -12103,11 +12103,11 @@
         <v>100</v>
       </c>
       <c r="H166" t="n">
-        <v>3315</v>
+        <v>3311</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>CLS1211</t>
+          <t>CLS1217</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -12171,11 +12171,11 @@
         <v>90</v>
       </c>
       <c r="H167" t="n">
-        <v>304</v>
+        <v>3410</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1219</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -12201,12 +12201,12 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -12239,11 +12239,11 @@
         <v>90</v>
       </c>
       <c r="H168" t="n">
-        <v>304</v>
+        <v>3103</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1191</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
@@ -12307,11 +12307,11 @@
         <v>90</v>
       </c>
       <c r="H169" t="n">
-        <v>3407</v>
+        <v>3501</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>CLS1215</t>
+          <t>CLS1221</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -12375,11 +12375,11 @@
         <v>90</v>
       </c>
       <c r="H170" t="n">
-        <v>304</v>
+        <v>3306</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1208</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -12405,12 +12405,12 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -12443,11 +12443,11 @@
         <v>90</v>
       </c>
       <c r="H171" t="n">
-        <v>501</v>
+        <v>3104</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>CLS1021</t>
+          <t>CLS1192</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -12511,11 +12511,11 @@
         <v>90</v>
       </c>
       <c r="H172" t="n">
-        <v>304</v>
+        <v>3502</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1222</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -12541,12 +12541,12 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -12579,11 +12579,11 @@
         <v>90</v>
       </c>
       <c r="H173" t="n">
-        <v>304</v>
+        <v>3504</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1223</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -12609,12 +12609,12 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>周五</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -12647,11 +12647,11 @@
         <v>90</v>
       </c>
       <c r="H174" t="n">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>CLS1029</t>
+          <t>CLS1038</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -12715,11 +12715,11 @@
         <v>90</v>
       </c>
       <c r="H175" t="n">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1021</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
@@ -13059,11 +13059,11 @@
         <v>125</v>
       </c>
       <c r="H180" t="n">
-        <v>3104</v>
+        <v>3201</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>CLS1192</t>
+          <t>CLS1196</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -13127,11 +13127,11 @@
         <v>90</v>
       </c>
       <c r="H181" t="n">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>CLS1196</t>
+          <t>CLS1197</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -13399,11 +13399,11 @@
         <v>60</v>
       </c>
       <c r="H185" t="n">
-        <v>304</v>
+        <v>3410</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1219</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
@@ -13535,11 +13535,11 @@
         <v>60</v>
       </c>
       <c r="H187" t="n">
-        <v>3403</v>
+        <v>3506</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>CLS1212</t>
+          <t>CLS1225</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -13671,11 +13671,11 @@
         <v>104</v>
       </c>
       <c r="H189" t="n">
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>CLS1201</t>
+          <t>CLS1202</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -13875,11 +13875,11 @@
         <v>100</v>
       </c>
       <c r="H192" t="n">
-        <v>3202</v>
+        <v>3211</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>CLS1197</t>
+          <t>CLS1201</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -13943,11 +13943,11 @@
         <v>100</v>
       </c>
       <c r="H193" t="n">
-        <v>305</v>
+        <v>1212</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>CLS1003</t>
+          <t>CLS1059</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
@@ -14011,11 +14011,11 @@
         <v>200</v>
       </c>
       <c r="H194" t="n">
-        <v>2103</v>
+        <v>301</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>CLS1006</t>
+          <t>CLS1248</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -14079,11 +14079,11 @@
         <v>200</v>
       </c>
       <c r="H195" t="n">
-        <v>301</v>
+        <v>1112</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>CLS1248</t>
+          <t>CLS1253</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -14121,37 +14121,37 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>62231003.001</t>
+          <t>62221001.001</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>生命科学导论-细胞治疗</t>
+          <t>侦探之旅：从柯南道尔到AI司鉴</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>新睿</t>
+          <t>新蒙</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>xkp01230781</t>
+          <t>xkp01231016</t>
         </is>
       </c>
       <c r="F196" t="n">
         <v>2</v>
       </c>
       <c r="G196" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="H196" t="n">
-        <v>201</v>
+        <v>305</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>CLS1023</t>
+          <t>CLS1261</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>10,11,12,13,14,15,16,17</t>
+          <t>1,2,3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -14189,37 +14189,37 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>62251001.001</t>
+          <t>62231003.001</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>“救”在你身边</t>
+          <t>生命科学导论-细胞治疗</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>新新</t>
+          <t>新睿</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>xkp01220242</t>
+          <t>xkp01230781</t>
         </is>
       </c>
       <c r="F197" t="n">
         <v>2</v>
       </c>
       <c r="G197" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H197" t="n">
-        <v>406</v>
+        <v>201</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>CLS1054</t>
+          <t>CLS1023</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -14257,7 +14257,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>62251001.002</t>
+          <t>62251001.001</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -14280,19 +14280,19 @@
         <v>2</v>
       </c>
       <c r="G198" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="H198" t="n">
-        <v>2408</v>
+        <v>1105</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>CLS1452</t>
+          <t>CLS1106</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -14318,49 +14318,49 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>62251004.001</t>
+          <t>62251001.002</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>家庭保健常用中医技能操作</t>
+          <t>“救”在你身边</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>新雪新</t>
+          <t>新新</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>xkp01220254</t>
+          <t>xkp01220242</t>
         </is>
       </c>
       <c r="F199" t="n">
         <v>2</v>
       </c>
       <c r="G199" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="H199" t="n">
-        <v>301</v>
+        <v>2408</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>CLS1248</t>
+          <t>CLS1452</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>12,13,14,15</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -14386,30 +14386,30 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>62251005.001</t>
+          <t>62251003.001</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>生活中的健康管理</t>
+          <t>数字时代的感官养护</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>新攀</t>
+          <t>新瑞中</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>xkp01220224</t>
+          <t>xkp01220236</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>10,11,12,13,14,15,16,17</t>
+          <t>11,12,13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -14454,30 +14454,30 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>62251005.001</t>
+          <t>62251004.001</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>生活中的健康管理</t>
+          <t>家庭保健常用中医技能操作</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>新荣荣</t>
+          <t>新雪新</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>xkp01220255</t>
+          <t>xkp01220254</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -14487,11 +14487,11 @@
         <v>210</v>
       </c>
       <c r="H201" t="n">
-        <v>301</v>
+        <v>1112</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>CLS1248</t>
+          <t>CLS1253</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -14512,7 +14512,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>10,11,12,13,14,15,16,17</t>
+          <t>12,13,14,15</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -14540,12 +14540,12 @@
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>新蕾</t>
+          <t>新攀</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>xkp01220241</t>
+          <t>xkp01220224</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -14608,12 +14608,12 @@
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>新长海</t>
+          <t>新荣荣</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>xkp01220217</t>
+          <t>xkp01220255</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -14676,12 +14676,12 @@
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>新新岭</t>
+          <t>新蕾</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>xkp01220229</t>
+          <t>xkp01220241</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -14733,37 +14733,37 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>62251006.001</t>
+          <t>62251005.001</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>中药美容</t>
+          <t>生活中的健康管理</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>新庆岭</t>
+          <t>新长海</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>xkp01220267</t>
+          <t>xkp01220217</t>
         </is>
       </c>
       <c r="F205" t="n">
         <v>2</v>
       </c>
       <c r="G205" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="H205" t="n">
-        <v>3308</v>
+        <v>301</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>CLS1209</t>
+          <t>CLS1248</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>9,10,11</t>
+          <t>10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -14794,49 +14794,49 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>62251006.002</t>
+          <t>62251005.001</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>中药美容</t>
+          <t>生活中的健康管理</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>新庆岭</t>
+          <t>新新岭</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>xkp01220267</t>
+          <t>xkp01220229</t>
         </is>
       </c>
       <c r="F206" t="n">
         <v>2</v>
       </c>
       <c r="G206" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="H206" t="n">
-        <v>2503</v>
+        <v>301</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>CLS1455</t>
+          <t>CLS1248</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>9,10,11</t>
+          <t>10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -14869,37 +14869,37 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>62251009.001</t>
+          <t>62251006.001</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>身边的医学</t>
+          <t>中药美容</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>新彩红</t>
+          <t>新庆岭</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>xkp01220193</t>
+          <t>xkp01220267</t>
         </is>
       </c>
       <c r="F207" t="n">
         <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="H207" t="n">
-        <v>3212</v>
+        <v>3314</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>CLS1202</t>
+          <t>CLS1210</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>10,11,12,13,14,15,16,17</t>
+          <t>9,10,11</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -14937,42 +14937,42 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>62251013.001</t>
+          <t>62251006.002</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>舌尖上的危险</t>
+          <t>中药美容</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>新莹利</t>
+          <t>新庆岭</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>xkp01230757</t>
+          <t>xkp01220267</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G208" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="H208" t="n">
-        <v>3103</v>
+        <v>2102</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>CLS1191</t>
+          <t>CLS1473</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>10,11,12,13</t>
+          <t>9,10,11</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -14998,49 +14998,49 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>62251013.002</t>
+          <t>62251009.001</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>舌尖上的危险</t>
+          <t>身边的医学</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>新莹利</t>
+          <t>新彩红</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>xkp01230757</t>
+          <t>xkp01220193</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G209" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H209" t="n">
-        <v>2102</v>
+        <v>3302</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>CLS1473</t>
+          <t>CLS1204</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>10,11,12,13</t>
+          <t>10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -15066,44 +15066,44 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>62251015.001</t>
+          <t>62251013.001</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>怀药与大健康</t>
+          <t>舌尖上的危险</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>新宝宝</t>
+          <t>新莹利</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>xkp01230580</t>
+          <t>xkp01230757</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G210" t="n">
         <v>70</v>
       </c>
       <c r="H210" t="n">
-        <v>3311</v>
+        <v>3103</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>CLS1217</t>
+          <t>CLS1191</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7</t>
+          <t>10,11,12,13</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -15141,42 +15141,42 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>62251016.001</t>
+          <t>62251013.002</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>解读心智密码：从正常到异常的心理全景图</t>
+          <t>舌尖上的危险</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>新志娟</t>
+          <t>新莹利</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>xkp01220247</t>
+          <t>xkp01230757</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G211" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H211" t="n">
-        <v>201</v>
+        <v>2203</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>CLS1023</t>
+          <t>CLS1477</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>10,11,12,13</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -15202,44 +15202,44 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>62251016.001</t>
+          <t>62251015.001</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>解读心智密码：从正常到异常的心理全景图</t>
+          <t>怀药与大健康</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>新婧茹</t>
+          <t>新宝宝</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>xkp01010215</t>
+          <t>xkp01230580</t>
         </is>
       </c>
       <c r="F212" t="n">
         <v>2</v>
       </c>
       <c r="G212" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H212" t="n">
-        <v>201</v>
+        <v>3507</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>CLS1023</t>
+          <t>CLS1226</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>2,3,4,5,6,7</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
@@ -15288,12 +15288,12 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>新晓阳</t>
+          <t>新志娟</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>xkp01230754</t>
+          <t>xkp01220247</t>
         </is>
       </c>
       <c r="F213" t="n">
@@ -15345,37 +15345,37 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>62251017.001</t>
+          <t>62251016.001</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>中药糕点烘焙</t>
+          <t>解读心智密码：从正常到异常的心理全景图</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>新超</t>
+          <t>新婧茹</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>xkp01960024</t>
+          <t>xkp01010215</t>
         </is>
       </c>
       <c r="F214" t="n">
         <v>2</v>
       </c>
       <c r="G214" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="H214" t="n">
-        <v>3614</v>
+        <v>201</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>CLS1175</t>
+          <t>CLS1023</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>12,13</t>
+          <t>7,8,9,10,11,12,13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -15406,49 +15406,49 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>62251017.002</t>
+          <t>62251016.001</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>中药糕点烘焙</t>
+          <t>解读心智密码：从正常到异常的心理全景图</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>新超</t>
+          <t>新晓阳</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>xkp01960024</t>
+          <t>xkp01230754</t>
         </is>
       </c>
       <c r="F215" t="n">
         <v>2</v>
       </c>
       <c r="G215" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="H215" t="n">
-        <v>2503</v>
+        <v>201</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>CLS1455</t>
+          <t>CLS1023</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>12,13</t>
+          <t>7,8,9,10,11,12,13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -15474,30 +15474,30 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>62251018.001</t>
+          <t>62251017.001</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>舌尖上的中药药膳</t>
+          <t>中药糕点烘焙</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>新庆岭</t>
+          <t>新超</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>xkp01220267</t>
+          <t>xkp01960024</t>
         </is>
       </c>
       <c r="F216" t="n">
@@ -15507,11 +15507,11 @@
         <v>110</v>
       </c>
       <c r="H216" t="n">
-        <v>501</v>
+        <v>3614</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>CLS1021</t>
+          <t>CLS1175</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>9,10,11</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -15542,30 +15542,30 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>62251018.002</t>
+          <t>62251017.002</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>舌尖上的中药药膳</t>
+          <t>中药糕点烘焙</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>新庆岭</t>
+          <t>新超</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>xkp01220267</t>
+          <t>xkp01960024</t>
         </is>
       </c>
       <c r="F217" t="n">
@@ -15575,11 +15575,11 @@
         <v>110</v>
       </c>
       <c r="H217" t="n">
-        <v>2403</v>
+        <v>2503</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>CLS1451</t>
+          <t>CLS1455</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>9,10,11</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -15610,44 +15610,44 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>62251020.001</t>
+          <t>62251018.001</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>吃瘦不饿瘦：科学体重管理全攻略</t>
+          <t>舌尖上的中药药膳</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>新新岭</t>
+          <t>新庆岭</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>xkp01220229</t>
+          <t>xkp01220267</t>
         </is>
       </c>
       <c r="F218" t="n">
         <v>2</v>
       </c>
       <c r="G218" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H218" t="n">
-        <v>2403</v>
+        <v>1212</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>CLS1016</t>
+          <t>CLS1059</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>11,12,13,14</t>
+          <t>9,10,11</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -15685,42 +15685,42 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>62251020.001</t>
+          <t>62251018.002</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>吃瘦不饿瘦：科学体重管理全攻略</t>
+          <t>舌尖上的中药药膳</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>新聪聪</t>
+          <t>新庆岭</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>xkp01230763</t>
+          <t>xkp01220267</t>
         </is>
       </c>
       <c r="F219" t="n">
         <v>2</v>
       </c>
       <c r="G219" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H219" t="n">
         <v>2403</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>CLS1016</t>
+          <t>CLS1451</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>11,12,13,14</t>
+          <t>9,10,11</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>第5-6节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
@@ -15764,12 +15764,12 @@
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>新书杰</t>
+          <t>新新岭</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>xkp01230765</t>
+          <t>xkp01220229</t>
         </is>
       </c>
       <c r="F220" t="n">
@@ -15779,11 +15779,11 @@
         <v>85</v>
       </c>
       <c r="H220" t="n">
-        <v>2403</v>
+        <v>301</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>CLS1016</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -15821,7 +15821,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>62251020.002</t>
+          <t>62251020.001</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -15832,12 +15832,12 @@
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>新新岭</t>
+          <t>新聪聪</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>xkp01220229</t>
+          <t>xkp01230763</t>
         </is>
       </c>
       <c r="F221" t="n">
@@ -15847,16 +15847,16 @@
         <v>85</v>
       </c>
       <c r="H221" t="n">
-        <v>2408</v>
+        <v>301</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>CLS1452</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -15882,14 +15882,14 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>62251020.002</t>
+          <t>62251020.001</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -15900,12 +15900,12 @@
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>新聪聪</t>
+          <t>新书杰</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>xkp01230763</t>
+          <t>xkp01230765</t>
         </is>
       </c>
       <c r="F222" t="n">
@@ -15915,16 +15915,16 @@
         <v>85</v>
       </c>
       <c r="H222" t="n">
-        <v>2408</v>
+        <v>301</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>CLS1452</t>
+          <t>CLS1005</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第5-6节</t>
         </is>
       </c>
     </row>
@@ -15968,12 +15968,12 @@
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>新书杰</t>
+          <t>新新岭</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>xkp01230765</t>
+          <t>xkp01220229</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -16025,42 +16025,42 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>62251021.001</t>
+          <t>62251020.002</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>医学人文与电影赏析</t>
+          <t>吃瘦不饿瘦：科学体重管理全攻略</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>新亚星</t>
+          <t>新聪聪</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>xkp01230527</t>
+          <t>xkp01230763</t>
         </is>
       </c>
       <c r="F224" t="n">
         <v>2</v>
       </c>
       <c r="G224" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H224" t="n">
-        <v>3302</v>
+        <v>2408</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>CLS1204</t>
+          <t>CLS1452</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>11,12,13,14,15,16,17,18</t>
+          <t>11,12,13,14</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -16086,49 +16086,49 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>62331003.001</t>
+          <t>62251020.002</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>网页设计基础</t>
+          <t>吃瘦不饿瘦：科学体重管理全攻略</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>新兵</t>
+          <t>新书杰</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>xkp01070058</t>
+          <t>xkp01230765</t>
         </is>
       </c>
       <c r="F225" t="n">
         <v>2</v>
       </c>
       <c r="G225" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H225" t="n">
-        <v>3314</v>
+        <v>2408</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>CLS1210</t>
+          <t>CLS1452</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>10,11,12,13,14</t>
+          <t>11,12,13,14</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -16154,30 +16154,30 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>62331003.002</t>
+          <t>62251021.001</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>网页设计基础</t>
+          <t>医学人文与电影赏析</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>新兵</t>
+          <t>新亚星</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>xkp01070058</t>
+          <t>xkp01230527</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -16187,16 +16187,16 @@
         <v>70</v>
       </c>
       <c r="H226" t="n">
-        <v>2203</v>
+        <v>3202</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>CLS1477</t>
+          <t>CLS1197</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>北校区</t>
+          <t>南校区</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>10,11,12,13,14</t>
+          <t>11,12,13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -16222,44 +16222,44 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>69771001.001</t>
+          <t>62331003.001</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>智能制造基础技术实训</t>
+          <t>网页设计基础</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>新伟涛</t>
+          <t>新兵</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>xkp01030007</t>
+          <t>xkp01070058</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G227" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H227" t="n">
-        <v>301</v>
+        <v>3304</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>CLS1005</t>
+          <t>CLS1206</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -16280,54 +16280,54 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>4,5,6,7,8,9,10,11,12,13,14,15</t>
+          <t>10,11,12,13,14</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>69851001.002</t>
+          <t>62331003.002</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>心学智慧与幸福</t>
+          <t>网页设计基础</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>新雪莹</t>
+          <t>新兵</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>xkp01230790</t>
+          <t>xkp01070058</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>1.9999999</v>
+        <v>2</v>
       </c>
       <c r="G228" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H228" t="n">
-        <v>2102</v>
+        <v>2508</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>CLS1473</t>
+          <t>CLS1478</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7,8,9,10</t>
+          <t>10,11,12,13,14</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -16358,44 +16358,44 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>69851002.001</t>
+          <t>69771001.001</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>反内耗行动：心理节能训练营</t>
+          <t>智能制造基础技术实训</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>新利霞</t>
+          <t>新伟涛</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>xkp01200443</t>
+          <t>xkp01030007</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G229" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H229" t="n">
-        <v>3410</v>
+        <v>3511</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>CLS1219</t>
+          <t>CLS1228</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -16416,7 +16416,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7,8,9</t>
+          <t>4,5,6,7,8,9,10,11,12,13,14,15</t>
         </is>
       </c>
       <c r="O229" t="inlineStr">
@@ -16433,37 +16433,37 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>69851002.002</t>
+          <t>69851001.002</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>反内耗行动：心理节能训练营</t>
+          <t>心学智慧与幸福</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>新革宇</t>
+          <t>新雪莹</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>xkp01010173</t>
+          <t>xkp01230790</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>2</v>
+        <v>1.9999999</v>
       </c>
       <c r="G230" t="n">
         <v>60</v>
       </c>
       <c r="H230" t="n">
-        <v>2508</v>
+        <v>2503</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>CLS1478</t>
+          <t>CLS1455</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2,3,4,5,6,7,8,9</t>
+          <t>2,3,4,5,6,7,8,9,10</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -16501,41 +16501,37 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>031010171.001</t>
+          <t>69851002.001</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Earth science（双语）</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>资源环境学院</t>
-        </is>
-      </c>
+          <t>反内耗行动：心理节能训练营</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>新永新</t>
+          <t>新利霞</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>xkp01100041</t>
+          <t>xkp01200443</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G231" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H231" t="n">
-        <v>406</v>
+        <v>3512</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>CLS1054</t>
+          <t>CLS1229</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -16545,27 +16541,23 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>水文2301 水文2302 水文2303</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>周三全天；周四全天</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
-          <t>周一全天；周二全天；周五全天</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8</t>
+          <t>2,3,4,5,6,7,8,9</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -16577,93 +16569,85 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>031010171.001</t>
+          <t>69851002.002</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Earth science（双语）</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>资源环境学院</t>
-        </is>
-      </c>
+          <t>反内耗行动：心理节能训练营</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>新永新</t>
+          <t>新革宇</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>xkp01100041</t>
+          <t>xkp01010173</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G232" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H232" t="n">
-        <v>406</v>
+        <v>2508</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>CLS1054</t>
+          <t>CLS1478</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>南校区</t>
+          <t>北校区</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>水文2301 水文2302 水文2303</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>周三全天；周四全天</t>
-        </is>
-      </c>
+          <t>全校</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
-          <t>周一全天；周二全天；周五全天</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8</t>
+          <t>2,3,4,5,6,7,8,9</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>051010540.001</t>
+          <t>031010171.001</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>三维激光扫描技术</t>
+          <t>Earth science（双语）</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>测绘与国土信息工程学院</t>
+          <t>资源环境学院</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -16673,21 +16657,21 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>xkp01110073</t>
+          <t>xkp01100041</t>
         </is>
       </c>
       <c r="F233" t="n">
         <v>4</v>
       </c>
       <c r="G233" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="H233" t="n">
-        <v>2104</v>
+        <v>406</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>CLS1007</t>
+          <t>CLS1054</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -16697,7 +16681,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>测绘2301 测绘2302 测绘2303 测绘2304</t>
+          <t>水文2301 水文2302 水文2303</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -16712,7 +16696,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>9,10,11,12,13,14,15,16</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -16722,24 +16706,24 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>051010540.001</t>
+          <t>031010171.001</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>三维激光扫描技术</t>
+          <t>Earth science（双语）</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>测绘与国土信息工程学院</t>
+          <t>资源环境学院</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -16749,21 +16733,21 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>xkp01110073</t>
+          <t>xkp01100041</t>
         </is>
       </c>
       <c r="F234" t="n">
         <v>4</v>
       </c>
       <c r="G234" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="H234" t="n">
-        <v>2104</v>
+        <v>406</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>CLS1007</t>
+          <t>CLS1054</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -16773,7 +16757,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>测绘2301 测绘2302 测绘2303 测绘2304</t>
+          <t>水文2301 水文2302 水文2303</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -16788,7 +16772,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>9,10,11,12,13,14,15,16</t>
+          <t>1,2,3,4,5,6,7,8</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -16798,14 +16782,14 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>第9-10节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>051011040.001</t>
+          <t>051010540.001</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -16832,14 +16816,14 @@
         <v>4</v>
       </c>
       <c r="G235" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H235" t="n">
-        <v>2203</v>
+        <v>305</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>CLS1009</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -16849,7 +16833,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>测绘卓2401 测绘卓2402 测绘卓2403 测绘卓2404</t>
+          <t>测绘2301 测绘2302 测绘2303 测绘2304</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -16864,7 +16848,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>5,6,7,8</t>
+          <t>9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -16874,14 +16858,14 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>051011040.001</t>
+          <t>051010540.001</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -16908,14 +16892,14 @@
         <v>4</v>
       </c>
       <c r="G236" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H236" t="n">
-        <v>2203</v>
+        <v>305</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>CLS1009</t>
+          <t>CLS1003</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -16925,7 +16909,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>测绘卓2401 测绘卓2402 测绘卓2403 测绘卓2404</t>
+          <t>测绘2301 测绘2302 测绘2303 测绘2304</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -16940,7 +16924,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>5,6,7,8</t>
+          <t>9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
@@ -16957,41 +16941,41 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>080070090.002</t>
+          <t>051011040.001</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>工程经济学（引）</t>
+          <t>三维激光扫描技术</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>电气工程与自动化学院</t>
+          <t>测绘与国土信息工程学院</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>新新</t>
+          <t>新永新</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>xkpwp0600946</t>
+          <t>xkp01110073</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G237" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="H237" t="n">
-        <v>1205</v>
+        <v>2203</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>CLS1058</t>
+          <t>CLS1009</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -17001,69 +16985,73 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>电气合2403 电气合2404</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr"/>
+          <t>测绘卓2401 测绘卓2402 测绘卓2403 测绘卓2404</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>周三全天；周四全天</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>周二(5-8节）</t>
+          <t>周一全天；周二全天；周五全天</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>11,12,13,14</t>
+          <t>5,6,7,8</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>080070090.002</t>
+          <t>051011040.001</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>工程经济学（引）</t>
+          <t>三维激光扫描技术</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>电气工程与自动化学院</t>
+          <t>测绘与国土信息工程学院</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>新新</t>
+          <t>新永新</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>xkpwp0600946</t>
+          <t>xkp01110073</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G238" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="H238" t="n">
-        <v>1205</v>
+        <v>2203</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>CLS1058</t>
+          <t>CLS1009</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -17073,28 +17061,32 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>电气合2403 电气合2404</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr"/>
+          <t>测绘卓2401 测绘卓2402 测绘卓2403 测绘卓2404</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>周三全天；周四全天</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>周二(5-8节）</t>
+          <t>周一全天；周二全天；周五全天</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>11,12,13,14</t>
+          <t>5,6,7,8</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第9-10节</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17153,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -17233,7 +17225,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>周四</t>
+          <t>周二</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -17245,41 +17237,41 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>110020140.001</t>
+          <t>080070090.002</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>微分方程数值解</t>
+          <t>工程经济学（引）</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>数学与信息科学学院</t>
+          <t>电气工程与自动化学院</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>新永新</t>
+          <t>新新</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>xkp01040034</t>
+          <t>xkpwp0600946</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="G241" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H241" t="n">
-        <v>2403</v>
+        <v>1205</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>CLS1016</t>
+          <t>CLS1058</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -17289,22 +17281,18 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>信息2301 信息2302</t>
-        </is>
-      </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>周三全天；周四全天</t>
-        </is>
-      </c>
+          <t>电气合2403 电气合2404</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
-          <t>周一全天；周二全天；周五全天</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9</t>
+          <t>11,12,13,14</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -17314,48 +17302,48 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>第7-8节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>110020140.001</t>
+          <t>080070090.002</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>微分方程数值解</t>
+          <t>工程经济学（引）</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>数学与信息科学学院</t>
+          <t>电气工程与自动化学院</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>新永新</t>
+          <t>新新</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>xkp01040034</t>
+          <t>xkpwp0600946</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="G242" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="H242" t="n">
-        <v>2403</v>
+        <v>1205</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>CLS1016</t>
+          <t>CLS1058</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -17365,22 +17353,18 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>信息2301 信息2302</t>
-        </is>
-      </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>周三全天；周四全天</t>
-        </is>
-      </c>
+          <t>电气合2403 电气合2404</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
-          <t>周一全天；周二全天；周五全天</t>
+          <t>周二(5-8节）</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9</t>
+          <t>11,12,13,14</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -17397,41 +17381,41 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>14712045.001</t>
+          <t>110020140.001</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>程序设计基础(Python)</t>
+          <t>微分方程数值解</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>外国语学院</t>
+          <t>数学与信息科学学院</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>新峰</t>
+          <t>新永新</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>xkp01230748</t>
+          <t>xkp01040034</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G243" t="n">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="H243" t="n">
-        <v>3501</v>
+        <v>2403</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>CLS1221</t>
+          <t>CLS1016</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -17441,69 +17425,73 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>英语2501 英语2502 英语2503 英语2504 英语2505</t>
-        </is>
-      </c>
-      <c r="L243" t="inlineStr"/>
+          <t>信息2301 信息2302</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>周三全天；周四全天</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>周二(5-8节）</t>
+          <t>周一全天；周二全天；周五全天</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>1,2,3,4,5,6,7,8,9</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第7-8节</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>14712045.001</t>
+          <t>110020140.001</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>程序设计基础(Python)</t>
+          <t>微分方程数值解</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>外国语学院</t>
+          <t>数学与信息科学学院</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>新峰</t>
+          <t>新永新</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>xkp01230748</t>
+          <t>xkp01040034</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G244" t="n">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="H244" t="n">
-        <v>3501</v>
+        <v>2403</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>CLS1221</t>
+          <t>CLS1016</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -17513,23 +17501,27 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>英语2501 英语2502 英语2503 英语2504 英语2505</t>
-        </is>
-      </c>
-      <c r="L244" t="inlineStr"/>
+          <t>信息2301 信息2302</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>周三全天；周四全天</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>周二(5-8节）</t>
+          <t>周一全天；周二全天；周五全天</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>1,2,3,4,5,6,7,8,9</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>周三</t>
+          <t>周四</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -17541,43 +17533,41 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>150013340.004</t>
+          <t>14712045.001</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>副项2</t>
+          <t>程序设计基础(Python)</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>体育学院</t>
+          <t>外国语学院</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>新燕</t>
+          <t>新峰</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>xkp01050051</t>
+          <t>xkp01230748</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>1.9999999</v>
+        <v>4</v>
       </c>
       <c r="G245" t="n">
-        <v>16</v>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>乒乓球训练房1</t>
-        </is>
+        <v>140</v>
+      </c>
+      <c r="H245" t="n">
+        <v>3601</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>CLS1315</t>
+          <t>CLS1232</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -17587,14 +17577,10 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>体育2301 体育2302 体育23034</t>
-        </is>
-      </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>英语2501 英语2502 英语2503 英语2504 英语2505</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
           <t>周二(5-8节）</t>
@@ -17602,7 +17588,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
@@ -17612,50 +17598,48 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>150013340.005</t>
+          <t>14712045.001</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>副项2</t>
+          <t>程序设计基础(Python)</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>体育学院</t>
+          <t>外国语学院</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>新朝阳</t>
+          <t>新峰</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>xkp01050055</t>
+          <t>xkp01230748</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G246" t="n">
-        <v>16</v>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>武术训练房1</t>
-        </is>
+        <v>140</v>
+      </c>
+      <c r="H246" t="n">
+        <v>3601</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>CLS1317</t>
+          <t>CLS1232</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -17665,14 +17649,10 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>体育2301 体育2302 体育23035</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>周一（3-4节）</t>
-        </is>
-      </c>
+          <t>英语2501 英语2502 英语2503 英语2504 英语2505</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
           <t>周二(5-8节）</t>
@@ -17685,24 +17665,24 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>周一</t>
+          <t>周三</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>150140600.001</t>
+          <t>150013340.004</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>体能训练理论与实践</t>
+          <t>副项2</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -17712,26 +17692,28 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>新建平</t>
+          <t>新燕</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>xkp01050048</t>
+          <t>xkp01050051</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>2</v>
+        <v>1.9999999</v>
       </c>
       <c r="G247" t="n">
-        <v>41</v>
-      </c>
-      <c r="H247" t="n">
-        <v>304</v>
+        <v>16</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>乒乓球训练房1</t>
+        </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>CLS1004</t>
+          <t>CLS1315</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -17741,12 +17723,12 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>民传2401</t>
+          <t>体育2301 体育2302 体育23034</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>周二（1-2节）</t>
+          <t>周一（3-4节）</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -17756,29 +17738,29 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>150140900.001</t>
+          <t>150013340.005</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>中国武术导论</t>
+          <t>副项2</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -17788,26 +17770,28 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>新柏利</t>
+          <t>新朝阳</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>xkp01050056</t>
+          <t>xkp01050055</t>
         </is>
       </c>
       <c r="F248" t="n">
         <v>2</v>
       </c>
       <c r="G248" t="n">
-        <v>41</v>
-      </c>
-      <c r="H248" t="n">
-        <v>2106</v>
+        <v>16</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>武术训练房1</t>
+        </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>CLS1008</t>
+          <t>CLS1317</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -17817,12 +17801,12 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>民传2401</t>
+          <t>体育2301 体育2302 体育23035</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>周二（1-2节）</t>
+          <t>周一（3-4节）</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -17837,24 +17821,24 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>周二</t>
+          <t>周一</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>第1-2节</t>
+          <t>第3-4节</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>151130360.001</t>
+          <t>150140600.001</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>瑜伽</t>
+          <t>体能训练理论与实践</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -17864,19 +17848,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>新辉</t>
+          <t>新建平</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>xkp01050082</t>
+          <t>xkp01050048</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>1.9999999</v>
+        <v>2</v>
       </c>
       <c r="G249" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H249" t="n">
         <v>301</v>
@@ -17893,7 +17877,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>体育2401</t>
+          <t>民传2401</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -17908,7 +17892,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17</t>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -17925,12 +17909,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>151140800.001</t>
+          <t>150140900.001</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>教育学</t>
+          <t>中国武术导论</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -17940,12 +17924,12 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>新斌</t>
+          <t>新柏利</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>xkp01180016</t>
+          <t>xkp01050056</t>
         </is>
       </c>
       <c r="F250" t="n">
@@ -17955,11 +17939,11 @@
         <v>41</v>
       </c>
       <c r="H250" t="n">
-        <v>2306</v>
+        <v>2103</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>CLS1014</t>
+          <t>CLS1006</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -17974,7 +17958,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>周二（3-4节）</t>
+          <t>周二（1-2节）</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -17994,81 +17978,233 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>第3-4节</t>
+          <t>第1-2节</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
+          <t>151130360.001</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>瑜伽</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>体育学院</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>新辉</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>xkp01050082</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>1.9999999</v>
+      </c>
+      <c r="G251" t="n">
+        <v>25</v>
+      </c>
+      <c r="H251" t="n">
+        <v>2104</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>CLS1007</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>体育2401</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>周二（1-2节）</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>第1-2节</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>151140800.001</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>教育学</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>体育学院</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>新斌</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>xkp01180016</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>2</v>
+      </c>
+      <c r="G252" t="n">
+        <v>41</v>
+      </c>
+      <c r="H252" t="n">
+        <v>2103</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>CLS1006</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>民传2401</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>周二（3-4节）</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>周二</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>第3-4节</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
           <t>151144030.001</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>足球</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>体育学院</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>新华伟</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>xkp01050027</t>
         </is>
       </c>
-      <c r="F251" t="n">
+      <c r="F253" t="n">
         <v>2</v>
       </c>
-      <c r="G251" t="n">
+      <c r="G253" t="n">
         <v>41</v>
       </c>
-      <c r="H251" t="n">
-        <v>2403</v>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>CLS1016</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>南校区</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
+      <c r="H253" t="n">
+        <v>2203</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>CLS1009</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>南校区</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
         <is>
           <t>民传2401</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t>周二（3-4节）</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>周二(5-8节）</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr">
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>周二(5-8节）</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
         <is>
           <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr">
+      <c r="O253" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
-      <c r="P251" t="inlineStr">
+      <c r="P253" t="inlineStr">
         <is>
           <t>第3-4节</t>
         </is>
